--- a/pacjenci/MARZENA SOBOLEWSKA.xlsx
+++ b/pacjenci/MARZENA SOBOLEWSKA.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -798,7 +798,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -806,17 +806,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/MARZENA SOBOLEWSKA.xlsx
+++ b/pacjenci/MARZENA SOBOLEWSKA.xlsx
@@ -413,38 +413,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -452,460 +452,335 @@
           <t>SUVmax</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>31.08.2020</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina.  Ocena zaawansowania klinicznego.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 98mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Drobny węzeł chłonny przedziału 3 po stronie lewej [SUV max 1,9].  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne: - położone lewobocznie od łuku aorty  łączące się z węzłami wnęki płuca lewego, wielkości wg PET do 39x71x61mm, SUV max do12,8; - przytchawicze dolne prawe średnicy wg PET 10mm, SUV max 3,7; - oskrzelowo-płucne prawe i lewe średnicy wg PET do 14mm, SUV max do 3,7; - pachowe lewe średnicy wg PET do 25mm, SUV max do 8,4. Aktywne metabolicznie zmiany naciekowo-guzkowe w miąższu obu płuc wielkości wg PET do 22x26mm, SUV max 4,2 (w segmencie 4 płuca prawego). Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywne metabolicznie węzły chłonne: - okolicy wnęki wątroby i głowy trzustki średnicy wg PET do 17mm, SUV max do 4,2; - okolicy wnęki śledziony średnicy wg PET 13mm, SUV max do 4,7; - okolicy krzywizny mniejszej żołądka średnicy wg PET do 16mm, SUV max do 3,9; - przyaortalne po stronie lewej na wysokości nerek średnicy wg PET do 14mm, SUV max do 6,2; - przyaortalne po stronie prawej na wysokości nerek średnicy wg PET do 10mm, SUV max do 3,7; - pomiędzy mięśniem pośladkowym średnim a wielkim po stronie lewej średnicy wg PET 11mm, SUV max 3,3. Drobny aktywny metabolicznie obszar we wstępnicy/kątnicy, średnicy wg PET 12mm, SUV max 4,3 - do ew. oceny endoskopowej. Wzmożona aktywność metaboliczna w topografii endometrium i jamy macicy, SUV max 3,7 - w pierwszej kolejności związana z fazą cyklu. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu w jamie Douglasa.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 2,6.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego, z zajęciem węzłów chłonnych po obu stronach przepony oraz z zajęciem miąższu płuc.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>12.8</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>21.11.2020</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina.  Ocena wczesnej odpowiedzi.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58min od podania 18F-FDG. Glikemia: 79mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Niejednorodnie miernie wzmożona  metabolicznie masa miękkotkankowa  położona w śródpiersiu środkowym po stronie lewej,  lewobocznie i poniżej od łuku aorty,  wielkości około 30x22x35mm, SUV max 3,7. Aktywne metabolicznie węzły chłonne pachowe lewe wielkości wg PET do 23x10mm, SUV max do 4,1. Aktywne metabolicznie zmiany guzkowo-naciekowe podopłucnowo w segmencie 6, 9 i 10 płuca prawego wielkości wg PET do 17x12mm, SUV max 3,3. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Bardzo wysokie ułożenie lewej kopuły przepony wraz z narządami nadbrzusza. Zmiany miąższowo- włókniste w segmencie 4 i 5 płuca prawego oraz 4 płuca lewego. Drobne zmiany włóknisto-guzkowe w segmencie 6 płuca prawego średnicy 11mm [lm TK 344]. Zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwiększona ilość płynu w jamie Douglasa.  Układ kostny: Rozlanie zwiększony metabolizm FDG w układzie kostnym, SUV max do 7,6 - w pierwszej kolejności związany ze stosowanym leczeniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Wartości referencyjne: MBPS SUVmax 1,7; Prawy płat wątroby SUVmax do 2,6.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - miernie niejednorodnie aktywnej metabolicznie masy miękkotkankowej w śródpiersiu środkowym po stronie lewej; - aktywnych metabolicznie zmian w miąższu płuca prawego (jedna ze zmian nie była widoczna w badaniu wyjściowym z 31.08.2020); - aktywnych metabolicznie węzłów chłonnych pachowych lewych.  W porównaniu do badania wyjściowego PET/CT z 31.08.2020 - częściowa regresja metaboliczna i radiologiczna większości zmian.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>7.6</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - wychwyt umiarkowanie większy od wątroby</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Częściowa odpowiedź metaboliczna na leczenie. Klasyfikacja Lugano: Partial Response (PR) - częściowa odpowiedź na leczenie. Deauville: 4 - wychwyt umiarkowanie większy od wątroby.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>10.12.2020</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina.  Wykluczenie progresji choroby. W badaniu fizykalnym badalne węzły chłonne szyjne o śr ok 1,5 cm- nowa lokalizacja.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 102 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Węzły chłonne szyjne wielkości do 11x6 mm.  Klatka piersiowa i śródpiersie: Niejednorodnie aktywna metabolicznie masa miękkotkankowa lewobocznie i poniżej od łuku aorty,  wielkości około 37x20x49 mm,  SUV max 5,4 [Im fuz. 117] - w porównaniu do poprzedniego badania PET/CT obraz zmiany podobnej rozległości w TK, o wyższej aktywności w PET, różnice w wymiarach mogą wynikać z fazy oddechowej. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie zmiany naciekowo- włókniste w  miąższu płuc: - w segmencie 1  płuca prawego przy pęczku naczyniowym wielkości 12 mm (SUV max 1,3) [Im CT 276] - w segmencie 4 i 5 płuca prawego (SUV max 2,1) - w segmencie 5 płuca lewego. - w segmencie 6, 8, 9,10 płuca prawego Bardzo wysokie ułożenie lewej kopuły przepony wraz z narządami nadbrzusza.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Rozlanie zwiększony metabolizm FDG w układzie kostnym, SUV max do 13,4 - w pierwszej kolejności związany ze stosowanym leczeniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 4,3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnej metabolicznie masy miękkotkankowej w śródpiersiu środkowym po stronie lewej. Zmiany w miąższu płuc stacjonarne w porównaniu do poprzednich badań - HRCT z dnia 24.11.2020 oraz PET/CT z dnia 5.11.2020r i mogą odpowiadać zejściu zmian zapalnych/włóknieniu w przebiegu sarkoidozy - do kontroli w HRCT.  Nie uwidoczniono nowych, aktywnych metabolicznie węzłów chłonnych szyjnych.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>13.4</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>03.02.2021</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina.  Ocena odpowiedzi po 2 cyklach chemioterapii II rzutu.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 93mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Pojedyncze drobne węzły chłonne szyjne.  Klatka piersiowa i śródpiersie: Miernie pobudzone metabolicznie zmiany guzkowo-włókniste w płacie dolnym płuca prawego, SUV max do 2,5.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa lewobocznie i poniżej od łuku aorty,  wielkości około 17x16mm. Nieaktywne metabolicznie zmiany naciekowo- włókniste w  miąższu płuc: - w segmencie 1  płuca prawego przy pęczku naczyniowym wielkości 12 mm (SUV max 1,3) [Im CT 107] - w segmencie 4 i 5 płuca prawego (SUV max 2,1) - w segmencie 5 płuca lewego. - w segmencie 6, 8, 9,10 płuca prawego Bardzo wysokie ułożenie lewej kopuły przepony wraz z narządami nadbrzusza.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 2,7.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech obecności aktywnej metabolicznie choroby chłoniakowej. Zmiany w płucach do dalszej kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>2.7</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>01.04.2021</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina.  Ocena odpowiedzi po III cyklach chemioterapii..</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 103mg%.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Pojedyncze drobne węzły chłonne szyjne.  Klatka piersiowa i śródpiersie:  Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa lewobocznie i poniżej od łuku aorty,  wielkości około 17x13mm. Nieaktywne metabolicznie zmiany naciekowo- włókniste w  miąższu płuc: - w segmencie 1  płuca prawego przy pęczku naczyniowym wielkości 12 mm (SUV max 1,3) [Im CT 278] - w segmencie 4 i 5 płuca prawego (SUV max do 1,8) - w segmencie 5 płuca lewego. - w segmencie 6, 8, 9,10 płuca prawego Płyka niedodmy wpłacie dolnym płuca lewego, drobne zmiany guzkowo-włokniste w płacie górnym płuca lewego. Bardzo wysokie ułożenie lewej kopuły przepony wraz z narządami nadbrzusza. Drobne węzły chłonne przytchawicze wielkości do 7mm.    Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w pętlach jelitowych w miednicy- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne pachwinowe do 12mm.  Nieaktywne metaboliczne drobne obszary miękkotkankowe w tkance podskórnej jamy brzusznej wielkości do 8mm.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Zwiększony metabolizm FDG w tkance tłuszczowej szyi i KLP.  Wartości referencyjne: MBPS SUVmax 1,9 Prawy płat wątroby SUVmax do 2,2.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech obecności aktywnej metabolicznie choroby chłoniakowej. Zmiany w płucach stacjonarne w porównaniu do poprzedniego badania z 3.02.2021 - do dalszej kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>2.2</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>02.11.2021</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina.  Ocena remisji choroby.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 79 mg%.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne zgrubienia błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Pojedyncze drobne węzły chłonne szyjne.  Klatka piersiowa i śródpiersie:  Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu,  lewobocznie i poniżej od łuku aorty,  wielkości około 21x16 mm z drobnymi zwapnieniami [Im CT 261]. Nieaktywne metabolicznie zmiany włókniste i miąższowo- włókniste w miąższu obu płuc, największe w płacie środkowym płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w pętlach jelitowych SUV max do 4,3- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie lewego nadnercza. Ok. 6mm zwapnienia  w grzbietowej części macicy - mięśniak?. Niewielka ilość płynu w grzbietowo-prawobocznej części miednicy, przypętlowo.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobna wyspa kostna w głowie prawej kości udowej.  Wartości referencyjne: MBPS SUVmax 1,9; Prawy płat wątroby SUVmax do 3,2.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono  obecności aktywnej metabolicznie choroby chłoniakowej.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>4.3</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>18.10.2022</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>7</v>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina.  Ocena pod kątem wykluczenia nawrotu.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 94 mg%.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne zgrubienia błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Pojedyncze drobne węzły chłonne szyjne.  Klatka piersiowa i śródpiersie:  Aktywny metabolicznie obszar miękkotkanowy w śródpiersiu,  lewobocznie i poniżej od łuku aorty,  wielkości 25x30mm wg PET, SUV max 6,5. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie obwodowe zmiany włókniste w płatach górnych i dolnych obu płuc. Niewielkie zmiany miąższowe i wydatne włókniste w segm 4 i 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Zmiana miąższowo-włóknista w piersi prawej wielkości 35x22mm [SUV max 1,7] - do weryfikacji.   Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w pętlach jelitowych - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie lewego nadnercza. Ok. 6mm zwapnienia  w grzbietowej części macicy - mięśniak?. Niewielka ilość płynu w grzbietowo-prawobocznej części miednicy, przypętlowo.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum.  Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobna wyspa kostna w głowie prawej kości udowej.  Inne: Pobudzony metabolicznie obszar w topografii mięśnia czworobocznego grzbietu po stronie prawej, wielkości 23x14mm wg PET, SUV max do 3,6- do kontroli/weryfikacji.  Wartości referencyjne: MBPS SUVmax do 2,1; Prawy płat wątroby SUVmax do 3,8.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie obszaru miękkotkanowego w śródpiersiu - wznowa choroby?  Pobudzony metabolicznie obszar w topografii mięśnia czworobocznego grzbietu po stronie prawej - do kontroli/weryfikacji. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>6.5</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>24.01.2023</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>8</v>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena pod kątem wykluczenia nawrotu.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 60min od podania 18F-FDG. Glikemia: 77 mg%.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne zgrubienia błony śluzowej w obu zatokach szczękowych. Pojedyncze drobne węzły chłonne szyjne.  Klatka piersiowa i śródpiersie:  Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie obwodowe zmiany włókniste w płatach górnych i dolnych obu płuc. Niewielkie zmiany miąższowe i wydatne włókniste w segm 4 i 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Zmiana miąższowo-włóknista w piersi prawej wielkości 35x22mm [SUV max 1,3] - do weryfikacji.   Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w pętlach jelitowych - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie lewego nadnercza. Ok. 6mm zwapnienia  w grzbietowej części macicy - mięśniak? Stan po założeniu pessarium.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum.  Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobna wyspa kostna w głowie prawej kości udowej.  Inne: Drobny aktywny metabolicznie obszar w topografii mięśni grzbietu przykręgosłupowo po stronie prawej na wysokości Th 9, SUV max 3,3 - w pierwszej kolejności czynnościowy.     Wartości referencyjne: MBPS SUVmax do 2,1; Prawy płat wątroby SUVmax do 3,4.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono  obecność aktywnego metabolicznie procesu chłoniakowego.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>3.4</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>28.03.2023</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>9</v>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina (stwardnienie guzkowe). Ocena remisji choroby przed autoPBSCT.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 61 min od podania 18F-FDG. Glikemia: 80 mg%.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie:  Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie obwodowe zmiany włókniste w płatach górnych i dolnych obu płuc. Niewielkie zmiany miąższowe i wydatne włókniste w segm 4 i 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Zmiana miąższowo-włóknista w piersi prawej wielkości 35x20mm (SUV max 1,2) - odszczepiona tkanka gruczołowa ?  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w pętlach jelitowych - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie lewego nadnercza. Ok. 6mm zwapnienia  w grzbietowej części macicy - mięśniak?  Układ kostny: Wzmożony metabolizm FDG w topografii kości krzyżowej SUV max do 5,3 - w porównaniu do poprzedniego badania PET/CT widoczna zmiana obrysu przedniego trzonu S3 -pourazowo.   Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum.  Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobna wyspa kostna w głowie prawej kości udowej.  Inne: Dość symetrycznie wzmożony metabolizm FDG w mięśniach szyi SUV max do 6,6- zmiany o charakterze odczynowo-przeciążeniowym. Wzmożony metabolizm FDG w tłuszczu brunatnym KLP.  Wartości referencyjne: MBPS SUVmax do 2,5 Prawy płat wątroby SUVmax do 3,6.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono  wzmożony metabolizm FDG w topografii kości krzyżowej - pourazowo.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>6.6</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>03.08.2023</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>10</v>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina (stwardnienie guzkowe). Ocena remisji choroby przed autoPBSCT.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 56 min od podania 18F-FDG. Glikemia: 92 mg%.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne zgrubienia błony śluzowej w zachyłkach zębodołowych obu zatok szczękowych.  Klatka piersiowa i śródpiersie:  Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobna zmiana miąższowo-włóknista w szczycie płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach górnych i dolnych obu płuc. Niewielkie zmiany miąższowe i wydatne włókniste w segm 4 i 5 płuca prawego. Zmiany miąższowo-włókniste w segm. 9 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Zmiana miąższowo-włóknista w piersi prawej wielkości 35x19mm (SUV max 1,2) - odszczepiona tkanka gruczołowa ?  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w pętlach jelitowych - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie lewego nadnercza. W grzbietowo-dolnej części trzonu macicy uwypukla się ok. 25mm obszar miękkotkankowy, z licznymi drobnymi zwapnieniami - mięśniak? Niewielka ilość płynu w jamie Douglasa po stronie prawej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych, zwłaszcza na poziomie L3/L4. Drobne obszary sklerotyczne w trzonach kręgowych, nieco wydatniejszy w trzonie Th6. Os sacrum arcuatum.  Miernie sklerotyczna przebudowa trzonu kręgu S3, z nieznacznie nierównym obrysem, zwłaszcza w jego części przedniej. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobna wyspa kostna w głowie prawej kości udowej.   Wartości referencyjne: MBPS SUVmax do 2,4; Prawy płat wątroby SUVmax do 3,9.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono  cech aktywnej metabolicznie choroby chłoniakowej. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>3.9</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/MARZENA SOBOLEWSKA.xlsx
+++ b/pacjenci/MARZENA SOBOLEWSKA.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 98mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Drobny węzeł chłonny przedziału 3 po stronie lewej [SUV max 1,9].  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne: - położone lewobocznie od łuku aorty  łączące się z węzłami wnęki płuca lewego, wielkości wg PET do 39x71x61mm, SUV max do12,8; - przytchawicze dolne prawe średnicy wg PET 10mm, SUV max 3,7; - oskrzelowo-płucne prawe i lewe średnicy wg PET do 14mm, SUV max do 3,7; - pachowe lewe średnicy wg PET do 25mm, SUV max do 8,4. Aktywne metabolicznie zmiany naciekowo-guzkowe w miąższu obu płuc wielkości wg PET do 22x26mm, SUV max 4,2 (w segmencie 4 płuca prawego). Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywne metabolicznie węzły chłonne: - okolicy wnęki wątroby i głowy trzustki średnicy wg PET do 17mm, SUV max do 4,2; - okolicy wnęki śledziony średnicy wg PET 13mm, SUV max do 4,7; - okolicy krzywizny mniejszej żołądka średnicy wg PET do 16mm, SUV max do 3,9; - przyaortalne po stronie lewej na wysokości nerek średnicy wg PET do 14mm, SUV max do 6,2; - przyaortalne po stronie prawej na wysokości nerek średnicy wg PET do 10mm, SUV max do 3,7; - pomiędzy mięśniem pośladkowym średnim a wielkim po stronie lewej średnicy wg PET 11mm, SUV max 3,3. Drobny aktywny metabolicznie obszar we wstępnicy/kątnicy, średnicy wg PET 12mm, SUV max 4,3 - do ew. oceny endoskopowej. Wzmożona aktywność metaboliczna w topografii endometrium i jamy macicy, SUV max 3,7 - w pierwszej kolejności związana z fazą cyklu. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu w jamie Douglasa.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 2,6.</t>
+          <t>98</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Drobny węzeł chłonny przedziału 3 po stronie lewej [SUV max 1,9].</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne: - położone lewobocznie od łuku aorty  łączące się z węzłami wnęki płuca lewego, wielkości wg PET do 39x71x61mm, SUV max do12,8; - przytchawicze dolne prawe średnicy wg PET 10mm, SUV max 3,7; - oskrzelowo-płucne prawe i lewe średnicy wg PET do 14mm, SUV max do 3,7; - pachowe lewe średnicy wg PET do 25mm, SUV max do 8,4. Aktywne metabolicznie zmiany naciekowo-guzkowe w miąższu obu płuc wielkości wg PET do 22x26mm, SUV max 4,2 (w segmencie 4 płuca prawego). Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne: - okolicy wnęki wątroby i głowy trzustki średnicy wg PET do 17mm, SUV max do 4,2; - okolicy wnęki śledziony średnicy wg PET 13mm, SUV max do 4,7; - okolicy krzywizny mniejszej żołądka średnicy wg PET do 16mm, SUV max do 3,9; - przyaortalne po stronie lewej na wysokości nerek średnicy wg PET do 14mm, SUV max do 6,2; - przyaortalne po stronie prawej na wysokości nerek średnicy wg PET do 10mm, SUV max do 3,7; - pomiędzy mięśniem pośladkowym średnim a wielkim po stronie lewej średnicy wg PET 11mm, SUV max 3,3. Drobny aktywny metabolicznie obszar we wstępnicy/kątnicy, średnicy wg PET 12mm, SUV max 4,3 - do ew. oceny endoskopowej. Wzmożona aktywność metaboliczna w topografii endometrium i jamy macicy, SUV max 3,7 - w pierwszej kolejności związana z fazą cyklu. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu w jamie Douglasa.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego, z zajęciem węzłów chłonnych po obu stronach przepony oraz z zajęciem miąższu płuc.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>12.8</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58min od podania 18F-FDG. Glikemia: 79mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Niejednorodnie miernie wzmożona  metabolicznie masa miękkotkankowa  położona w śródpiersiu środkowym po stronie lewej,  lewobocznie i poniżej od łuku aorty,  wielkości około 30x22x35mm, SUV max 3,7. Aktywne metabolicznie węzły chłonne pachowe lewe wielkości wg PET do 23x10mm, SUV max do 4,1. Aktywne metabolicznie zmiany guzkowo-naciekowe podopłucnowo w segmencie 6, 9 i 10 płuca prawego wielkości wg PET do 17x12mm, SUV max 3,3. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Bardzo wysokie ułożenie lewej kopuły przepony wraz z narządami nadbrzusza. Zmiany miąższowo- włókniste w segmencie 4 i 5 płuca prawego oraz 4 płuca lewego. Drobne zmiany włóknisto-guzkowe w segmencie 6 płuca prawego średnicy 11mm [lm TK 344]. Zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwiększona ilość płynu w jamie Douglasa.  Układ kostny: Rozlanie zwiększony metabolizm FDG w układzie kostnym, SUV max do 7,6 - w pierwszej kolejności związany ze stosowanym leczeniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Wartości referencyjne: MBPS SUVmax 1,7; Prawy płat wątroby SUVmax do 2,6.</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne zgrubienie błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Niejednorodnie miernie wzmożona  metabolicznie masa miękkotkankowa  położona w śródpiersiu środkowym po stronie lewej,  lewobocznie i poniżej od łuku aorty,  wielkości około 30x22x35mm, SUV max 3,7. Aktywne metabolicznie węzły chłonne pachowe lewe wielkości wg PET do 23x10mm, SUV max do 4,1. Aktywne metabolicznie zmiany guzkowo-naciekowe podopłucnowo w segmencie 6, 9 i 10 płuca prawego wielkości wg PET do 17x12mm, SUV max 3,3. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Bardzo wysokie ułożenie lewej kopuły przepony wraz z narządami nadbrzusza. Zmiany miąższowo- włókniste w segmencie 4 i 5 płuca prawego oraz 4 płuca lewego. Drobne zmiany włóknisto-guzkowe w segmencie 6 płuca prawego średnicy 11mm [lm TK 344]. Zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zwiększona ilość płynu w jamie Douglasa.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Rozlanie zwiększony metabolizm FDG w układzie kostnym, SUV max do 7,6 - w pierwszej kolejności związany ze stosowanym leczeniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - miernie niejednorodnie aktywnej metabolicznie masy miękkotkankowej w śródpiersiu środkowym po stronie lewej; - aktywnych metabolicznie zmian w miąższu płuca prawego (jedna ze zmian nie była widoczna w badaniu wyjściowym z 31.08.2020); - aktywnych metabolicznie węzłów chłonnych pachowych lewych.  W porównaniu do badania wyjściowego PET/CT z 31.08.2020 - częściowa regresja metaboliczna i radiologiczna większości zmian.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>7.6</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 102 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Węzły chłonne szyjne wielkości do 11x6 mm.  Klatka piersiowa i śródpiersie: Niejednorodnie aktywna metabolicznie masa miękkotkankowa lewobocznie i poniżej od łuku aorty,  wielkości około 37x20x49 mm,  SUV max 5,4 [Im fuz. 117] - w porównaniu do poprzedniego badania PET/CT obraz zmiany podobnej rozległości w TK, o wyższej aktywności w PET, różnice w wymiarach mogą wynikać z fazy oddechowej. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie zmiany naciekowo- włókniste w  miąższu płuc: - w segmencie 1  płuca prawego przy pęczku naczyniowym wielkości 12 mm (SUV max 1,3) [Im CT 276] - w segmencie 4 i 5 płuca prawego (SUV max 2,1) - w segmencie 5 płuca lewego. - w segmencie 6, 8, 9,10 płuca prawego Bardzo wysokie ułożenie lewej kopuły przepony wraz z narządami nadbrzusza.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Rozlanie zwiększony metabolizm FDG w układzie kostnym, SUV max do 13,4 - w pierwszej kolejności związany ze stosowanym leczeniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 4,3</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Węzły chłonne szyjne wielkości do 11x6 mm.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Niejednorodnie aktywna metabolicznie masa miękkotkankowa lewobocznie i poniżej od łuku aorty,  wielkości około 37x20x49 mm,  SUV max 5,4 [Im fuz. 117] - w porównaniu do poprzedniego badania PET/CT obraz zmiany podobnej rozległości w TK, o wyższej aktywności w PET, różnice w wymiarach mogą wynikać z fazy oddechowej. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie zmiany naciekowo- włókniste w  miąższu płuc: - w segmencie 1  płuca prawego przy pęczku naczyniowym wielkości 12 mm (SUV max 1,3) [Im CT 276] - w segmencie 4 i 5 płuca prawego (SUV max 2,1) - w segmencie 5 płuca lewego. - w segmencie 6, 8, 9,10 płuca prawego Bardzo wysokie ułożenie lewej kopuły przepony wraz z narządami nadbrzusza.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Rozlanie zwiększony metabolizm FDG w układzie kostnym, SUV max do 13,4 - w pierwszej kolejności związany ze stosowanym leczeniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnej metabolicznie masy miękkotkankowej w śródpiersiu środkowym po stronie lewej. Zmiany w miąższu płuc stacjonarne w porównaniu do poprzednich badań - HRCT z dnia 24.11.2020 oraz PET/CT z dnia 5.11.2020r i mogą odpowiadać zejściu zmian zapalnych/włóknieniu w przebiegu sarkoidozy - do kontroli w HRCT.  Nie uwidoczniono nowych, aktywnych metabolicznie węzłów chłonnych szyjnych.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>13.4</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 93mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Pojedyncze drobne węzły chłonne szyjne.  Klatka piersiowa i śródpiersie: Miernie pobudzone metabolicznie zmiany guzkowo-włókniste w płacie dolnym płuca prawego, SUV max do 2,5.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa lewobocznie i poniżej od łuku aorty,  wielkości około 17x16mm. Nieaktywne metabolicznie zmiany naciekowo- włókniste w  miąższu płuc: - w segmencie 1  płuca prawego przy pęczku naczyniowym wielkości 12 mm (SUV max 1,3) [Im CT 107] - w segmencie 4 i 5 płuca prawego (SUV max 2,1) - w segmencie 5 płuca lewego. - w segmencie 6, 8, 9,10 płuca prawego Bardzo wysokie ułożenie lewej kopuły przepony wraz z narządami nadbrzusza.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 2,7.</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Pojedyncze drobne węzły chłonne szyjne.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Miernie pobudzone metabolicznie zmiany guzkowo-włókniste w płacie dolnym płuca prawego, SUV max do 2,5.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa lewobocznie i poniżej od łuku aorty,  wielkości około 17x16mm. Nieaktywne metabolicznie zmiany naciekowo- włókniste w  miąższu płuc: - w segmencie 1  płuca prawego przy pęczku naczyniowym wielkości 12 mm (SUV max 1,3) [Im CT 107] - w segmencie 4 i 5 płuca prawego (SUV max 2,1) - w segmencie 5 płuca lewego. - w segmencie 6, 8, 9,10 płuca prawego Bardzo wysokie ułożenie lewej kopuły przepony wraz z narządami nadbrzusza.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech obecności aktywnej metabolicznie choroby chłoniakowej. Zmiany w płucach do dalszej kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>2.7</v>
       </c>
     </row>
@@ -601,20 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 103mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Pojedyncze drobne węzły chłonne szyjne.  Klatka piersiowa i śródpiersie:  Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa lewobocznie i poniżej od łuku aorty,  wielkości około 17x13mm. Nieaktywne metabolicznie zmiany naciekowo- włókniste w  miąższu płuc: - w segmencie 1  płuca prawego przy pęczku naczyniowym wielkości 12 mm (SUV max 1,3) [Im CT 278] - w segmencie 4 i 5 płuca prawego (SUV max do 1,8) - w segmencie 5 płuca lewego. - w segmencie 6, 8, 9,10 płuca prawego Płyka niedodmy wpłacie dolnym płuca lewego, drobne zmiany guzkowo-włokniste w płacie górnym płuca lewego. Bardzo wysokie ułożenie lewej kopuły przepony wraz z narządami nadbrzusza. Drobne węzły chłonne przytchawicze wielkości do 7mm.    Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w pętlach jelitowych w miednicy- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne pachwinowe do 12mm.  Nieaktywne metaboliczne drobne obszary miękkotkankowe w tkance podskórnej jamy brzusznej wielkości do 8mm.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Zwiększony metabolizm FDG w tkance tłuszczowej szyi i KLP.  Wartości referencyjne: MBPS SUVmax 1,9 Prawy płat wątroby SUVmax do 2,2.</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Pojedyncze drobne węzły chłonne szyjne.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa lewobocznie i poniżej od łuku aorty,  wielkości około 17x13mm. Nieaktywne metabolicznie zmiany naciekowo- włókniste w  miąższu płuc: - w segmencie 1  płuca prawego przy pęczku naczyniowym wielkości 12 mm (SUV max 1,3) [Im CT 278] - w segmencie 4 i 5 płuca prawego (SUV max do 1,8) - w segmencie 5 płuca lewego. - w segmencie 6, 8, 9,10 płuca prawego Płyka niedodmy wpłacie dolnym płuca lewego, drobne zmiany guzkowo-włokniste w płacie górnym płuca lewego. Bardzo wysokie ułożenie lewej kopuły przepony wraz z narządami nadbrzusza. Drobne węzły chłonne przytchawicze wielkości do 7mm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Odcinkowe pobudzenie metaboliczne w pętlach jelitowych w miednicy- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne pachwinowe do 12mm.  Nieaktywne metaboliczne drobne obszary miękkotkankowe w tkance podskórnej jamy brzusznej wielkości do 8mm.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Zwiększony metabolizm FDG w tkance tłuszczowej szyi i KLP.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech obecności aktywnej metabolicznie choroby chłoniakowej. Zmiany w płucach stacjonarne w porównaniu do poprzedniego badania z 3.02.2021 - do dalszej kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="L6" t="n">
         <v>2.2</v>
       </c>
     </row>
@@ -634,20 +784,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 79 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne zgrubienia błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Pojedyncze drobne węzły chłonne szyjne.  Klatka piersiowa i śródpiersie:  Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu,  lewobocznie i poniżej od łuku aorty,  wielkości około 21x16 mm z drobnymi zwapnieniami [Im CT 261]. Nieaktywne metabolicznie zmiany włókniste i miąższowo- włókniste w miąższu obu płuc, największe w płacie środkowym płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w pętlach jelitowych SUV max do 4,3- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie lewego nadnercza. Ok. 6mm zwapnienia  w grzbietowej części macicy - mięśniak?. Niewielka ilość płynu w grzbietowo-prawobocznej części miednicy, przypętlowo.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobna wyspa kostna w głowie prawej kości udowej.  Wartości referencyjne: MBPS SUVmax 1,9; Prawy płat wątroby SUVmax do 3,2.</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne zgrubienia błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Pojedyncze drobne węzły chłonne szyjne.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu,  lewobocznie i poniżej od łuku aorty,  wielkości około 21x16 mm z drobnymi zwapnieniami [Im CT 261]. Nieaktywne metabolicznie zmiany włókniste i miąższowo- włókniste w miąższu obu płuc, największe w płacie środkowym płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Odcinkowe pobudzenie metaboliczne w pętlach jelitowych SUV max do 4,3- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie lewego nadnercza. Ok. 6mm zwapnienia  w grzbietowej części macicy - mięśniak?. Niewielka ilość płynu w grzbietowo-prawobocznej części miednicy, przypętlowo.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobna wyspa kostna w głowie prawej kości udowej.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono  obecności aktywnej metabolicznie choroby chłoniakowej.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="L7" t="n">
         <v>4.3</v>
       </c>
     </row>
@@ -667,20 +842,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 94 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne zgrubienia błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Pojedyncze drobne węzły chłonne szyjne.  Klatka piersiowa i śródpiersie:  Aktywny metabolicznie obszar miękkotkanowy w śródpiersiu,  lewobocznie i poniżej od łuku aorty,  wielkości 25x30mm wg PET, SUV max 6,5. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie obwodowe zmiany włókniste w płatach górnych i dolnych obu płuc. Niewielkie zmiany miąższowe i wydatne włókniste w segm 4 i 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Zmiana miąższowo-włóknista w piersi prawej wielkości 35x22mm [SUV max 1,7] - do weryfikacji.   Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w pętlach jelitowych - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie lewego nadnercza. Ok. 6mm zwapnienia  w grzbietowej części macicy - mięśniak?. Niewielka ilość płynu w grzbietowo-prawobocznej części miednicy, przypętlowo.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum.  Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobna wyspa kostna w głowie prawej kości udowej.  Inne: Pobudzony metabolicznie obszar w topografii mięśnia czworobocznego grzbietu po stronie prawej, wielkości 23x14mm wg PET, SUV max do 3,6- do kontroli/weryfikacji.  Wartości referencyjne: MBPS SUVmax do 2,1; Prawy płat wątroby SUVmax do 3,8.</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne zgrubienia błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Pojedyncze drobne węzły chłonne szyjne.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar miękkotkanowy w śródpiersiu,  lewobocznie i poniżej od łuku aorty,  wielkości 25x30mm wg PET, SUV max 6,5. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie obwodowe zmiany włókniste w płatach górnych i dolnych obu płuc. Niewielkie zmiany miąższowe i wydatne włókniste w segm 4 i 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Zmiana miąższowo-włóknista w piersi prawej wielkości 35x22mm [SUV max 1,7] - do weryfikacji.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Odcinkowe pobudzenie metaboliczne w pętlach jelitowych - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie lewego nadnercza. Ok. 6mm zwapnienia  w grzbietowej części macicy - mięśniak?. Niewielka ilość płynu w grzbietowo-prawobocznej części miednicy, przypętlowo.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum.  Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobna wyspa kostna w głowie prawej kości udowej.  Inne: Pobudzony metabolicznie obszar w topografii mięśnia czworobocznego grzbietu po stronie prawej, wielkości 23x14mm wg PET, SUV max do 3,6- do kontroli/weryfikacji.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie obszaru miękkotkanowego w śródpiersiu - wznowa choroby?  Pobudzony metabolicznie obszar w topografii mięśnia czworobocznego grzbietu po stronie prawej - do kontroli/weryfikacji. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="L8" t="n">
         <v>6.5</v>
       </c>
     </row>
@@ -700,20 +900,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 60min od podania 18F-FDG. Glikemia: 77 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne zgrubienia błony śluzowej w obu zatokach szczękowych. Pojedyncze drobne węzły chłonne szyjne.  Klatka piersiowa i śródpiersie:  Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie obwodowe zmiany włókniste w płatach górnych i dolnych obu płuc. Niewielkie zmiany miąższowe i wydatne włókniste w segm 4 i 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Zmiana miąższowo-włóknista w piersi prawej wielkości 35x22mm [SUV max 1,3] - do weryfikacji.   Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w pętlach jelitowych - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie lewego nadnercza. Ok. 6mm zwapnienia  w grzbietowej części macicy - mięśniak? Stan po założeniu pessarium.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum.  Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobna wyspa kostna w głowie prawej kości udowej.  Inne: Drobny aktywny metabolicznie obszar w topografii mięśni grzbietu przykręgosłupowo po stronie prawej na wysokości Th 9, SUV max 3,3 - w pierwszej kolejności czynnościowy.     Wartości referencyjne: MBPS SUVmax do 2,1; Prawy płat wątroby SUVmax do 3,4.</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne zgrubienia błony śluzowej w obu zatokach szczękowych. Pojedyncze drobne węzły chłonne szyjne.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie obwodowe zmiany włókniste w płatach górnych i dolnych obu płuc. Niewielkie zmiany miąższowe i wydatne włókniste w segm 4 i 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Zmiana miąższowo-włóknista w piersi prawej wielkości 35x22mm [SUV max 1,3] - do weryfikacji.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Odcinkowe pobudzenie metaboliczne w pętlach jelitowych - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie lewego nadnercza. Ok. 6mm zwapnienia  w grzbietowej części macicy - mięśniak? Stan po założeniu pessarium.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum.  Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobna wyspa kostna w głowie prawej kości udowej.  Inne: Drobny aktywny metabolicznie obszar w topografii mięśni grzbietu przykręgosłupowo po stronie prawej na wysokości Th 9, SUV max 3,3 - w pierwszej kolejności czynnościowy.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono  obecność aktywnego metabolicznie procesu chłoniakowego.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="L9" t="n">
         <v>3.4</v>
       </c>
     </row>
@@ -733,20 +958,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 61 min od podania 18F-FDG. Glikemia: 80 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie:  Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie obwodowe zmiany włókniste w płatach górnych i dolnych obu płuc. Niewielkie zmiany miąższowe i wydatne włókniste w segm 4 i 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Zmiana miąższowo-włóknista w piersi prawej wielkości 35x20mm (SUV max 1,2) - odszczepiona tkanka gruczołowa ?  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w pętlach jelitowych - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie lewego nadnercza. Ok. 6mm zwapnienia  w grzbietowej części macicy - mięśniak?  Układ kostny: Wzmożony metabolizm FDG w topografii kości krzyżowej SUV max do 5,3 - w porównaniu do poprzedniego badania PET/CT widoczna zmiana obrysu przedniego trzonu S3 -pourazowo.   Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum.  Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobna wyspa kostna w głowie prawej kości udowej.  Inne: Dość symetrycznie wzmożony metabolizm FDG w mięśniach szyi SUV max do 6,6- zmiany o charakterze odczynowo-przeciążeniowym. Wzmożony metabolizm FDG w tłuszczu brunatnym KLP.  Wartości referencyjne: MBPS SUVmax do 2,5 Prawy płat wątroby SUVmax do 3,6.</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie obwodowe zmiany włókniste w płatach górnych i dolnych obu płuc. Niewielkie zmiany miąższowe i wydatne włókniste w segm 4 i 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Zmiana miąższowo-włóknista w piersi prawej wielkości 35x20mm (SUV max 1,2) - odszczepiona tkanka gruczołowa ?</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Odcinkowe pobudzenie metaboliczne w pętlach jelitowych - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie lewego nadnercza. Ok. 6mm zwapnienia  w grzbietowej części macicy - mięśniak?</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG w topografii kości krzyżowej SUV max do 5,3 - w porównaniu do poprzedniego badania PET/CT widoczna zmiana obrysu przedniego trzonu S3 -pourazowo.   Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych. Os sacrum arcuatum.  Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobna wyspa kostna w głowie prawej kości udowej.  Inne: Dość symetrycznie wzmożony metabolizm FDG w mięśniach szyi SUV max do 6,6- zmiany o charakterze odczynowo-przeciążeniowym. Wzmożony metabolizm FDG w tłuszczu brunatnym KLP.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono  wzmożony metabolizm FDG w topografii kości krzyżowej - pourazowo.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="L10" t="n">
         <v>6.6</v>
       </c>
     </row>
@@ -766,20 +1016,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 56 min od podania 18F-FDG. Glikemia: 92 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne zgrubienia błony śluzowej w zachyłkach zębodołowych obu zatok szczękowych.  Klatka piersiowa i śródpiersie:  Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobna zmiana miąższowo-włóknista w szczycie płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach górnych i dolnych obu płuc. Niewielkie zmiany miąższowe i wydatne włókniste w segm 4 i 5 płuca prawego. Zmiany miąższowo-włókniste w segm. 9 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Zmiana miąższowo-włóknista w piersi prawej wielkości 35x19mm (SUV max 1,2) - odszczepiona tkanka gruczołowa ?  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w pętlach jelitowych - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie lewego nadnercza. W grzbietowo-dolnej części trzonu macicy uwypukla się ok. 25mm obszar miękkotkankowy, z licznymi drobnymi zwapnieniami - mięśniak? Niewielka ilość płynu w jamie Douglasa po stronie prawej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych, zwłaszcza na poziomie L3/L4. Drobne obszary sklerotyczne w trzonach kręgowych, nieco wydatniejszy w trzonie Th6. Os sacrum arcuatum.  Miernie sklerotyczna przebudowa trzonu kręgu S3, z nieznacznie nierównym obrysem, zwłaszcza w jego części przedniej. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobna wyspa kostna w głowie prawej kości udowej.   Wartości referencyjne: MBPS SUVmax do 2,4; Prawy płat wątroby SUVmax do 3,9.</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Drobne zgrubienia błony śluzowej w zachyłkach zębodołowych obu zatok szczękowych.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobna zmiana miąższowo-włóknista w szczycie płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach górnych i dolnych obu płuc. Niewielkie zmiany miąższowe i wydatne włókniste w segm 4 i 5 płuca prawego. Zmiany miąższowo-włókniste w segm. 9 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Zmiana miąższowo-włóknista w piersi prawej wielkości 35x19mm (SUV max 1,2) - odszczepiona tkanka gruczołowa ?</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Odcinkowe pobudzenie metaboliczne w pętlach jelitowych - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Mierne pogrubienie lewego nadnercza. W grzbietowo-dolnej części trzonu macicy uwypukla się ok. 25mm obszar miękkotkankowy, z licznymi drobnymi zwapnieniami - mięśniak? Niewielka ilość płynu w jamie Douglasa po stronie prawej.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Zniesienie fizjologicznej lordozy szyjnej, z nieznacznie łukowato kyfotycznym ustawieniem i niewielkimi dyskopatiami. Nieliczne drobne guzki Schmorla ze sklerotyzacją blaszek granicznych, zwłaszcza na poziomie L3/L4. Drobne obszary sklerotyczne w trzonach kręgowych, nieco wydatniejszy w trzonie Th6. Os sacrum arcuatum.  Miernie sklerotyczna przebudowa trzonu kręgu S3, z nieznacznie nierównym obrysem, zwłaszcza w jego części przedniej. Drobne zmiany wytwórcze na krawędziach trzonów kręgowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobna wyspa kostna w głowie prawej kości udowej.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono  cech aktywnej metabolicznie choroby chłoniakowej. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="L11" t="n">
         <v>3.9</v>
       </c>
     </row>
